--- a/data/processed/positivacao/2025-06_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2025-06_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -26453,7 +26453,7 @@
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr"/>
@@ -37727,7 +37727,7 @@
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1439" t="inlineStr"/>
@@ -66125,7 +66125,7 @@
     <row r="2532">
       <c r="A2532" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2532" t="inlineStr"/>
@@ -67796,12 +67796,12 @@
       <c r="A2597" t="inlineStr"/>
       <c r="B2597" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 7 cliente(s), não positivou 85 cliente(s) - Total vendido: R$ 2.780,09
+          <t>Vendedor 1 - VENDEDOR 01: positivou 7 cliente(s), não positivou 85 cliente(s) - Total vendido: R$ 2.780,09
 Vendedor 18 - LOJA: positivou 227 cliente(s), não positivou 676 cliente(s) - Total vendido: R$ 62.274,44
-Vendedor 3 - FERNANDA: positivou 113 cliente(s), não positivou 320 cliente(s) - Total vendido: R$ 104.294,10
-Vendedor 4 - DANIELA: positivou 128 cliente(s), não positivou 518 cliente(s) - Total vendido: R$ 57.628,54
+Vendedor 3 - VENDEDOR 03: positivou 113 cliente(s), não positivou 320 cliente(s) - Total vendido: R$ 104.294,10
+Vendedor 4 - VENDEDOR 04: positivou 128 cliente(s), não positivou 518 cliente(s) - Total vendido: R$ 57.628,54
 Vendedor 5 - SITE: positivou 0 cliente(s), não positivou 445 cliente(s) - Total vendido: R$ 0,00
-Vendedor 8 - RAFAEL: positivou 1 cliente(s), não positivou 62 cliente(s) - Total vendido: R$ 611,45</t>
+Vendedor 8 - VENDEDOR 08: positivou 1 cliente(s), não positivou 62 cliente(s) - Total vendido: R$ 611,45</t>
         </is>
       </c>
       <c r="C2597" t="inlineStr"/>
